--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_metropolitana.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>17.90434633920825</v>
+      </c>
+      <c r="C2">
         <v>17.011076420334</v>
-      </c>
-      <c r="C2">
-        <v>17.90434633920825</v>
       </c>
       <c r="D2">
         <v>5.87852276534753</v>
       </c>
       <c r="E2">
-        <v>12.60869667262029</v>
+        <v>13.27079289601968</v>
       </c>
       <c r="F2">
         <v>74.12051043136003</v>
       </c>
       <c r="G2">
-        <v>13.27079289601968</v>
+        <v>12.60869667262029</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.8478685663334</v>
+      </c>
+      <c r="C3">
         <v>26.81982887822276</v>
-      </c>
-      <c r="C3">
-        <v>28.8478685663334</v>
       </c>
       <c r="D3">
         <v>3.728584565325034</v>
       </c>
       <c r="E3">
-        <v>17.22889804275233</v>
+        <v>18.53169863748263</v>
       </c>
       <c r="F3">
         <v>64.23940331976503</v>
       </c>
       <c r="G3">
-        <v>18.53169863748263</v>
+        <v>17.22889804275233</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>28.44462850618969</v>
+      </c>
+      <c r="C4">
         <v>27.37794094602762</v>
-      </c>
-      <c r="C4">
-        <v>28.44462850618969</v>
       </c>
       <c r="D4">
         <v>3.652575633687653</v>
       </c>
       <c r="E4">
-        <v>17.56994576733829</v>
+        <v>18.25449843766835</v>
       </c>
       <c r="F4">
         <v>64.17555579499336</v>
       </c>
       <c r="G4">
-        <v>18.25449843766835</v>
+        <v>17.56994576733829</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>28.29371536231175</v>
+      </c>
+      <c r="C5">
         <v>30.75031502709844</v>
-      </c>
-      <c r="C5">
-        <v>28.29371536231175</v>
       </c>
       <c r="D5">
         <v>3.251999204296797</v>
       </c>
       <c r="E5">
-        <v>19.33446665794878</v>
+        <v>17.78986315489881</v>
       </c>
       <c r="F5">
         <v>62.8756701871524</v>
       </c>
       <c r="G5">
-        <v>17.78986315489881</v>
+        <v>19.33446665794878</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>31.43961201807199</v>
+      </c>
+      <c r="C6">
         <v>28.87908742278906</v>
-      </c>
-      <c r="C6">
-        <v>31.43961201807199</v>
       </c>
       <c r="D6">
         <v>3.462713296164893</v>
       </c>
       <c r="E6">
-        <v>18.01354896435028</v>
+        <v>19.61069552567669</v>
       </c>
       <c r="F6">
-        <v>62.37575550997305</v>
+        <v>62.37575550997304</v>
       </c>
       <c r="G6">
-        <v>19.61069552567669</v>
+        <v>18.01354896435027</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>23.10023222006155</v>
+      </c>
+      <c r="C7">
         <v>23.68455830989107</v>
-      </c>
-      <c r="C7">
-        <v>23.10023222006155</v>
       </c>
       <c r="D7">
         <v>4.222160223196493</v>
       </c>
       <c r="E7">
-        <v>16.13556706003409</v>
+        <v>15.73748352037043</v>
       </c>
       <c r="F7">
         <v>68.12694941959549</v>
       </c>
       <c r="G7">
-        <v>15.73748352037043</v>
+        <v>16.13556706003409</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>34.62498277630633</v>
+      </c>
+      <c r="C8">
         <v>20.36682640047767</v>
-      </c>
-      <c r="C8">
-        <v>34.62498277630633</v>
       </c>
       <c r="D8">
         <v>4.909945125159738</v>
       </c>
       <c r="E8">
-        <v>13.14058240151725</v>
+        <v>22.3398790943933</v>
       </c>
       <c r="F8">
         <v>64.51953850408945</v>
       </c>
       <c r="G8">
-        <v>22.3398790943933</v>
+        <v>13.14058240151725</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>23.4043950558905</v>
+      </c>
+      <c r="C9">
         <v>21.56545953685095</v>
-      </c>
-      <c r="C9">
-        <v>23.4043950558905</v>
       </c>
       <c r="D9">
         <v>4.637044707028871</v>
       </c>
       <c r="E9">
-        <v>14.87582338923773</v>
+        <v>16.14431850100121</v>
       </c>
       <c r="F9">
         <v>68.97985810976107</v>
       </c>
       <c r="G9">
-        <v>16.14431850100121</v>
+        <v>14.87582338923773</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>25.98780763151953</v>
+      </c>
+      <c r="C10">
         <v>30.75533633221599</v>
-      </c>
-      <c r="C10">
-        <v>25.98780763151953</v>
       </c>
       <c r="D10">
         <v>3.251468262932008</v>
       </c>
       <c r="E10">
-        <v>19.62148745678575</v>
+        <v>16.57986880595692</v>
       </c>
       <c r="F10">
         <v>63.79864373725734</v>
       </c>
       <c r="G10">
-        <v>16.57986880595692</v>
+        <v>19.62148745678575</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>27.23876511525036</v>
+      </c>
+      <c r="C11">
         <v>30.10349101515795</v>
-      </c>
-      <c r="C11">
-        <v>27.23876511525036</v>
       </c>
       <c r="D11">
         <v>3.321873863388376</v>
       </c>
       <c r="E11">
-        <v>19.13248974274755</v>
+        <v>17.31179263927317</v>
       </c>
       <c r="F11">
         <v>63.55571761797928</v>
       </c>
       <c r="G11">
-        <v>17.31179263927317</v>
+        <v>19.13248974274755</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>29.3876870172197</v>
+      </c>
+      <c r="C12">
         <v>29.17211999897349</v>
-      </c>
-      <c r="C12">
-        <v>29.3876870172197</v>
       </c>
       <c r="D12">
         <v>3.427930503628766</v>
       </c>
       <c r="E12">
-        <v>18.39818081766096</v>
+        <v>18.5341339462014</v>
       </c>
       <c r="F12">
         <v>63.06768523613763</v>
       </c>
       <c r="G12">
-        <v>18.5341339462014</v>
+        <v>18.39818081766096</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>34.07992363431249</v>
+      </c>
+      <c r="C13">
         <v>23.64038703518896</v>
-      </c>
-      <c r="C13">
-        <v>34.07992363431249</v>
       </c>
       <c r="D13">
         <v>4.230049188752662</v>
       </c>
       <c r="E13">
+        <v>21.60782177618584</v>
+      </c>
+      <c r="F13">
+        <v>63.40337498418149</v>
+      </c>
+      <c r="G13">
         <v>14.98880323963268</v>
-      </c>
-      <c r="F13">
-        <v>63.40337498418148</v>
-      </c>
-      <c r="G13">
-        <v>21.60782177618584</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>27.89426012278171</v>
+      </c>
+      <c r="C14">
         <v>32.81559260625986</v>
-      </c>
-      <c r="C14">
-        <v>27.89426012278171</v>
       </c>
       <c r="D14">
         <v>3.047331833980781</v>
       </c>
       <c r="E14">
-        <v>20.41915417692982</v>
+        <v>17.35690727675031</v>
       </c>
       <c r="F14">
         <v>62.22393854631988</v>
       </c>
       <c r="G14">
-        <v>17.35690727675031</v>
+        <v>20.41915417692982</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>24.58574486640767</v>
+      </c>
+      <c r="C15">
         <v>33.11715425883348</v>
-      </c>
-      <c r="C15">
-        <v>24.58574486640767</v>
       </c>
       <c r="D15">
         <v>3.019583120531154</v>
       </c>
       <c r="E15">
+        <v>15.58991305979903</v>
+      </c>
+      <c r="F15">
+        <v>63.41037517679627</v>
+      </c>
+      <c r="G15">
         <v>20.99971176340468</v>
-      </c>
-      <c r="F15">
-        <v>63.41037517679629</v>
-      </c>
-      <c r="G15">
-        <v>15.58991305979904</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>32.75970647828706</v>
+      </c>
+      <c r="C16">
         <v>18.05624007447566</v>
-      </c>
-      <c r="C16">
-        <v>32.75970647828706</v>
       </c>
       <c r="D16">
         <v>5.538251573280764</v>
       </c>
       <c r="E16">
-        <v>11.97236796717561</v>
+        <v>21.72164630271782</v>
       </c>
       <c r="F16">
         <v>66.30598573010657</v>
       </c>
       <c r="G16">
-        <v>21.72164630271782</v>
+        <v>11.97236796717561</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>27.14382075195026</v>
+      </c>
+      <c r="C17">
         <v>26.43263534518154</v>
-      </c>
-      <c r="C17">
-        <v>27.14382075195026</v>
       </c>
       <c r="D17">
         <v>3.783202041495617</v>
       </c>
       <c r="E17">
-        <v>17.21138514126398</v>
+        <v>17.67446745533881</v>
       </c>
       <c r="F17">
         <v>65.11414740339721</v>
       </c>
       <c r="G17">
-        <v>17.67446745533881</v>
+        <v>17.21138514126398</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>27.74949572567477</v>
+      </c>
+      <c r="C18">
         <v>30.49979188678641</v>
-      </c>
-      <c r="C18">
-        <v>27.74949572567477</v>
       </c>
       <c r="D18">
         <v>3.278710896493807</v>
       </c>
       <c r="E18">
-        <v>19.27325699024805</v>
+        <v>17.53530530490026</v>
       </c>
       <c r="F18">
         <v>63.19143770485171</v>
       </c>
       <c r="G18">
-        <v>17.53530530490026</v>
+        <v>19.27325699024805</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>24.04632581820015</v>
+      </c>
+      <c r="C19">
         <v>30.48228755781275</v>
-      </c>
-      <c r="C19">
-        <v>24.04632581820015</v>
       </c>
       <c r="D19">
         <v>3.280593682817926</v>
       </c>
       <c r="E19">
-        <v>19.72598271081389</v>
+        <v>15.5610830207144</v>
       </c>
       <c r="F19">
         <v>64.7129342684717</v>
       </c>
       <c r="G19">
-        <v>15.5610830207144</v>
+        <v>19.72598271081389</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>28.20028636052375</v>
+      </c>
+      <c r="C20">
         <v>23.14866142759318</v>
-      </c>
-      <c r="C20">
-        <v>28.20028636052375</v>
       </c>
       <c r="D20">
         <v>4.319904211860825</v>
       </c>
       <c r="E20">
-        <v>15.2948941937809</v>
+        <v>18.63262795853932</v>
       </c>
       <c r="F20">
         <v>66.07247784767978</v>
       </c>
       <c r="G20">
-        <v>18.63262795853932</v>
+        <v>15.2948941937809</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>22.98061627290403</v>
+      </c>
+      <c r="C21">
         <v>30.41448182407353</v>
-      </c>
-      <c r="C21">
-        <v>22.98061627290403</v>
       </c>
       <c r="D21">
         <v>3.287907404716936</v>
       </c>
       <c r="E21">
-        <v>19.82754481818269</v>
+        <v>14.98132375675754</v>
       </c>
       <c r="F21">
         <v>65.19113142505977</v>
       </c>
       <c r="G21">
-        <v>14.98132375675754</v>
+        <v>19.82754481818269</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>27.62838009157755</v>
+      </c>
+      <c r="C22">
         <v>33.48248243769297</v>
-      </c>
-      <c r="C22">
-        <v>27.62838009157755</v>
       </c>
       <c r="D22">
         <v>2.986636375785113</v>
       </c>
       <c r="E22">
-        <v>20.78226254397334</v>
+        <v>17.14867617107943</v>
       </c>
       <c r="F22">
         <v>62.06906128494723</v>
       </c>
       <c r="G22">
-        <v>17.14867617107943</v>
+        <v>20.78226254397334</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>29.16918476059936</v>
+      </c>
+      <c r="C23">
         <v>23.34506713186505</v>
-      </c>
-      <c r="C23">
-        <v>29.16918476059936</v>
       </c>
       <c r="D23">
         <v>4.283560181478516</v>
       </c>
       <c r="E23">
-        <v>15.30681024375697</v>
+        <v>19.12554689063821</v>
       </c>
       <c r="F23">
         <v>65.56764286560481</v>
       </c>
       <c r="G23">
-        <v>19.12554689063821</v>
+        <v>15.30681024375697</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>18.45074806902858</v>
+      </c>
+      <c r="C24">
         <v>29.4947372516975</v>
-      </c>
-      <c r="C24">
-        <v>18.45074806902858</v>
       </c>
       <c r="D24">
         <v>3.390435356200528</v>
       </c>
       <c r="E24">
-        <v>19.93621987704245</v>
+        <v>12.47131538284512</v>
       </c>
       <c r="F24">
         <v>67.59246474011243</v>
       </c>
       <c r="G24">
-        <v>12.47131538284512</v>
+        <v>19.93621987704245</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>30.87879055186499</v>
+      </c>
+      <c r="C25">
         <v>21.36755036539936</v>
-      </c>
-      <c r="C25">
-        <v>30.87879055186499</v>
       </c>
       <c r="D25">
         <v>4.67999364877739</v>
       </c>
       <c r="E25">
-        <v>14.03485314435976</v>
+        <v>20.28212327851317</v>
       </c>
       <c r="F25">
         <v>65.68302357712707</v>
       </c>
       <c r="G25">
-        <v>20.28212327851317</v>
+        <v>14.03485314435976</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>30.4505666248502</v>
+      </c>
+      <c r="C26">
         <v>14.09028152529663</v>
-      </c>
-      <c r="C26">
-        <v>30.4505666248502</v>
       </c>
       <c r="D26">
         <v>7.097090276050734</v>
       </c>
       <c r="E26">
-        <v>9.748304168424319</v>
+        <v>21.06710110986662</v>
       </c>
       <c r="F26">
         <v>69.18459472170908</v>
       </c>
       <c r="G26">
-        <v>21.06710110986662</v>
+        <v>9.748304168424319</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>24.51154956689124</v>
+      </c>
+      <c r="C27">
         <v>26.5555822906641</v>
-      </c>
-      <c r="C27">
-        <v>24.51154956689124</v>
       </c>
       <c r="D27">
         <v>3.765686585421103</v>
       </c>
       <c r="E27">
-        <v>17.57866318379829</v>
+        <v>16.22560067533667</v>
       </c>
       <c r="F27">
         <v>66.19573614086504</v>
       </c>
       <c r="G27">
-        <v>16.22560067533667</v>
+        <v>17.57866318379829</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>27.44135149311773</v>
+      </c>
+      <c r="C28">
         <v>27.0497585327473</v>
-      </c>
-      <c r="C28">
-        <v>27.44135149311773</v>
       </c>
       <c r="D28">
         <v>3.696890672016048</v>
       </c>
       <c r="E28">
-        <v>17.50894179491532</v>
+        <v>17.76241460659029</v>
       </c>
       <c r="F28">
         <v>64.72864359849439</v>
       </c>
       <c r="G28">
-        <v>17.76241460659029</v>
+        <v>17.50894179491532</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>31.6482001691747</v>
+      </c>
+      <c r="C29">
         <v>24.04891446234819</v>
-      </c>
-      <c r="C29">
-        <v>31.6482001691747</v>
       </c>
       <c r="D29">
         <v>4.158191845064918</v>
       </c>
       <c r="E29">
-        <v>15.4459602666774</v>
+        <v>20.3267737132279</v>
       </c>
       <c r="F29">
         <v>64.2272660200947</v>
       </c>
       <c r="G29">
-        <v>20.3267737132279</v>
+        <v>15.4459602666774</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>25.98364350569902</v>
+      </c>
+      <c r="C30">
         <v>32.5713181788911</v>
-      </c>
-      <c r="C30">
-        <v>25.98364350569902</v>
       </c>
       <c r="D30">
         <v>3.070185844207197</v>
       </c>
       <c r="E30">
-        <v>20.54260417512794</v>
+        <v>16.38778328324263</v>
       </c>
       <c r="F30">
-        <v>63.06961254162945</v>
+        <v>63.06961254162943</v>
       </c>
       <c r="G30">
-        <v>16.38778328324263</v>
+        <v>20.54260417512793</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>23.75023941773606</v>
+      </c>
+      <c r="C31">
         <v>25.32465045010535</v>
-      </c>
-      <c r="C31">
-        <v>23.75023941773606</v>
       </c>
       <c r="D31">
         <v>3.948721827257601</v>
       </c>
       <c r="E31">
-        <v>16.98787131257067</v>
+        <v>15.93175043683832</v>
       </c>
       <c r="F31">
-        <v>67.08037825059102</v>
+        <v>67.08037825059101</v>
       </c>
       <c r="G31">
-        <v>15.93175043683832</v>
+        <v>16.98787131257066</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>28.36925565205162</v>
+      </c>
+      <c r="C32">
         <v>30.12376498716641</v>
-      </c>
-      <c r="C32">
-        <v>28.36925565205162</v>
       </c>
       <c r="D32">
         <v>3.319638167493435</v>
       </c>
       <c r="E32">
-        <v>19.00636688333296</v>
+        <v>17.8993721853717</v>
       </c>
       <c r="F32">
         <v>63.09426093129534</v>
       </c>
       <c r="G32">
-        <v>17.8993721853717</v>
+        <v>19.00636688333296</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>30.14242353490544</v>
+      </c>
+      <c r="C33">
         <v>34.49954201763681</v>
-      </c>
-      <c r="C33">
-        <v>30.14242353490544</v>
       </c>
       <c r="D33">
         <v>2.898589202977771</v>
       </c>
       <c r="E33">
-        <v>20.95428216120692</v>
+        <v>18.30786181016897</v>
       </c>
       <c r="F33">
         <v>60.7378560286241</v>
       </c>
       <c r="G33">
-        <v>18.30786181016897</v>
+        <v>20.95428216120692</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>29.98784083413467</v>
+      </c>
+      <c r="C34">
         <v>19.93123051288368</v>
-      </c>
-      <c r="C34">
-        <v>29.98784083413467</v>
       </c>
       <c r="D34">
         <v>5.017251691277131</v>
       </c>
       <c r="E34">
+        <v>20.00268582555563</v>
+      </c>
+      <c r="F34">
+        <v>66.70265437312479</v>
+      </c>
+      <c r="G34">
         <v>13.29465980131959</v>
-      </c>
-      <c r="F34">
-        <v>66.70265437312477</v>
-      </c>
-      <c r="G34">
-        <v>20.00268582555563</v>
       </c>
     </row>
     <row r="35">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="B35">
+        <v>21.42507145773785</v>
+      </c>
+      <c r="C35">
         <v>21.13924050632911</v>
-      </c>
-      <c r="C35">
-        <v>21.42507145773785</v>
       </c>
       <c r="D35">
         <v>4.730538922155689</v>
       </c>
       <c r="E35">
-        <v>14.82786274846766</v>
+        <v>15.02835538752363</v>
       </c>
       <c r="F35">
         <v>70.1437818640087</v>
       </c>
       <c r="G35">
-        <v>15.02835538752363</v>
+        <v>14.82786274846766</v>
       </c>
     </row>
     <row r="36">
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B36">
+        <v>27.91042174973859</v>
+      </c>
+      <c r="C36">
         <v>28.59881491808992</v>
-      </c>
-      <c r="C36">
-        <v>27.91042174973859</v>
       </c>
       <c r="D36">
         <v>3.496648385131018</v>
       </c>
       <c r="E36">
-        <v>18.27292467011859</v>
+        <v>17.83308279049051</v>
       </c>
       <c r="F36">
         <v>63.89399253939091</v>
       </c>
       <c r="G36">
-        <v>17.83308279049051</v>
+        <v>18.27292467011859</v>
       </c>
     </row>
     <row r="37">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B37">
+        <v>39.39722052856212</v>
+      </c>
+      <c r="C37">
         <v>14.85503437545992</v>
-      </c>
-      <c r="C37">
-        <v>39.39722052856212</v>
       </c>
       <c r="D37">
         <v>6.731724577170759</v>
       </c>
       <c r="E37">
-        <v>9.630351520438344</v>
+        <v>25.54077446263306</v>
       </c>
       <c r="F37">
         <v>64.82887401692859</v>
       </c>
       <c r="G37">
-        <v>25.54077446263306</v>
+        <v>9.630351520438344</v>
       </c>
     </row>
     <row r="38">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B38">
+        <v>38.78202607697268</v>
+      </c>
+      <c r="C38">
         <v>14.42883880404523</v>
-      </c>
-      <c r="C38">
-        <v>38.78202607697268</v>
       </c>
       <c r="D38">
         <v>6.930564639197732</v>
       </c>
       <c r="E38">
-        <v>9.417634196667795</v>
+        <v>25.31284325500704</v>
       </c>
       <c r="F38">
-        <v>65.26952254832517</v>
+        <v>65.26952254832518</v>
       </c>
       <c r="G38">
-        <v>25.31284325500703</v>
+        <v>9.417634196667796</v>
       </c>
     </row>
     <row r="39">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B39">
+        <v>32.22268041237113</v>
+      </c>
+      <c r="C39">
         <v>24.17319587628866</v>
-      </c>
-      <c r="C39">
-        <v>32.22268041237113</v>
       </c>
       <c r="D39">
         <v>4.136813374274992</v>
       </c>
       <c r="E39">
-        <v>15.45641512418921</v>
+        <v>20.60328007171861</v>
       </c>
       <c r="F39">
         <v>63.94030480409218</v>
       </c>
       <c r="G39">
-        <v>20.60328007171861</v>
+        <v>15.45641512418921</v>
       </c>
     </row>
     <row r="40">
@@ -1348,22 +1348,22 @@
         </is>
       </c>
       <c r="B40">
+        <v>32.20757569481837</v>
+      </c>
+      <c r="C40">
         <v>21.26496292921344</v>
-      </c>
-      <c r="C40">
-        <v>32.20757569481837</v>
       </c>
       <c r="D40">
         <v>4.702571094663031</v>
       </c>
       <c r="E40">
-        <v>13.8558748815038</v>
+        <v>20.9858884094689</v>
       </c>
       <c r="F40">
         <v>65.15823670902731</v>
       </c>
       <c r="G40">
-        <v>20.9858884094689</v>
+        <v>13.8558748815038</v>
       </c>
     </row>
     <row r="41">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="B41">
+        <v>32.15087147643786</v>
+      </c>
+      <c r="C41">
         <v>20.17152869570564</v>
-      </c>
-      <c r="C41">
-        <v>32.15087147643786</v>
       </c>
       <c r="D41">
         <v>4.957482474855227</v>
       </c>
       <c r="E41">
-        <v>13.24265418146594</v>
+        <v>21.1071197933484</v>
       </c>
       <c r="F41">
         <v>65.65022602518566</v>
       </c>
       <c r="G41">
-        <v>21.1071197933484</v>
+        <v>13.24265418146594</v>
       </c>
     </row>
     <row r="42">
@@ -1398,22 +1398,22 @@
         </is>
       </c>
       <c r="B42">
+        <v>16.16042197162605</v>
+      </c>
+      <c r="C42">
         <v>18.59767188068389</v>
-      </c>
-      <c r="C42">
-        <v>16.16042197162605</v>
       </c>
       <c r="D42">
         <v>5.377017114914425</v>
       </c>
       <c r="E42">
-        <v>13.80078283169119</v>
+        <v>11.99217168308814</v>
       </c>
       <c r="F42">
         <v>74.20704548522068</v>
       </c>
       <c r="G42">
-        <v>11.99217168308814</v>
+        <v>13.80078283169119</v>
       </c>
     </row>
     <row r="43">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="B43">
+        <v>32.05607888018312</v>
+      </c>
+      <c r="C43">
         <v>22.78809754379787</v>
-      </c>
-      <c r="C43">
-        <v>32.05607888018312</v>
       </c>
       <c r="D43">
         <v>4.388255746571374</v>
       </c>
       <c r="E43">
-        <v>14.71679340487527</v>
+        <v>20.70215336507711</v>
       </c>
       <c r="F43">
         <v>64.58105323004762</v>
       </c>
       <c r="G43">
-        <v>20.70215336507711</v>
+        <v>14.71679340487527</v>
       </c>
     </row>
     <row r="44">
@@ -1448,22 +1448,22 @@
         </is>
       </c>
       <c r="B44">
+        <v>29.0051741484214</v>
+      </c>
+      <c r="C44">
         <v>25.70545681023332</v>
-      </c>
-      <c r="C44">
-        <v>29.0051741484214</v>
       </c>
       <c r="D44">
         <v>3.890224582983878</v>
       </c>
       <c r="E44">
-        <v>16.61518452284182</v>
+        <v>18.74801619558569</v>
       </c>
       <c r="F44">
-        <v>64.63679928157249</v>
+        <v>64.63679928157248</v>
       </c>
       <c r="G44">
-        <v>18.74801619558569</v>
+        <v>16.61518452284181</v>
       </c>
     </row>
     <row r="45">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="B45">
+        <v>32.00406917599186</v>
+      </c>
+      <c r="C45">
         <v>24.61851475076297</v>
-      </c>
-      <c r="C45">
-        <v>32.00406917599186</v>
       </c>
       <c r="D45">
         <v>4.06198347107438</v>
       </c>
       <c r="E45">
-        <v>15.71836840737854</v>
+        <v>20.4338789295921</v>
       </c>
       <c r="F45">
         <v>63.84775266302936</v>
       </c>
       <c r="G45">
-        <v>20.4338789295921</v>
+        <v>15.71836840737854</v>
       </c>
     </row>
     <row r="46">
@@ -1498,22 +1498,22 @@
         </is>
       </c>
       <c r="B46">
+        <v>31.20049038098831</v>
+      </c>
+      <c r="C46">
         <v>27.42832893247831</v>
-      </c>
-      <c r="C46">
-        <v>31.20049038098831</v>
       </c>
       <c r="D46">
         <v>3.645865566443184</v>
       </c>
       <c r="E46">
-        <v>17.29088639200999</v>
+        <v>19.66886629807978</v>
       </c>
       <c r="F46">
         <v>63.04024730991024</v>
       </c>
       <c r="G46">
-        <v>19.66886629807978</v>
+        <v>17.29088639200999</v>
       </c>
     </row>
     <row r="47">
@@ -1523,22 +1523,22 @@
         </is>
       </c>
       <c r="B47">
+        <v>28.98397976391231</v>
+      </c>
+      <c r="C47">
         <v>29.2685497470489</v>
-      </c>
-      <c r="C47">
-        <v>28.98397976391231</v>
       </c>
       <c r="D47">
         <v>3.416636658264314</v>
       </c>
       <c r="E47">
-        <v>18.4948384948385</v>
+        <v>18.31501831501831</v>
       </c>
       <c r="F47">
         <v>63.19014319014319</v>
       </c>
       <c r="G47">
-        <v>18.31501831501831</v>
+        <v>18.4948384948385</v>
       </c>
     </row>
     <row r="48">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B48">
+        <v>36.0046233866307</v>
+      </c>
+      <c r="C48">
         <v>36.44769793874013</v>
-      </c>
-      <c r="C48">
-        <v>36.0046233866307</v>
       </c>
       <c r="D48">
         <v>2.743657505285412</v>
       </c>
       <c r="E48">
-        <v>21.13494191242181</v>
+        <v>20.87801608579088</v>
       </c>
       <c r="F48">
         <v>57.98704200178731</v>
       </c>
       <c r="G48">
-        <v>20.87801608579088</v>
+        <v>21.13494191242181</v>
       </c>
     </row>
     <row r="49">
@@ -1573,22 +1573,22 @@
         </is>
       </c>
       <c r="B49">
+        <v>30.19659455457761</v>
+      </c>
+      <c r="C49">
         <v>22.80373447396562</v>
-      </c>
-      <c r="C49">
-        <v>30.19659455457761</v>
       </c>
       <c r="D49">
         <v>4.385246640815223</v>
       </c>
       <c r="E49">
-        <v>14.9043695649252</v>
+        <v>19.73629386701792</v>
       </c>
       <c r="F49">
         <v>65.35933656805688</v>
       </c>
       <c r="G49">
-        <v>19.73629386701792</v>
+        <v>14.9043695649252</v>
       </c>
     </row>
     <row r="50">
@@ -1598,22 +1598,22 @@
         </is>
       </c>
       <c r="B50">
+        <v>32.93493250867149</v>
+      </c>
+      <c r="C50">
         <v>23.64077061306365</v>
-      </c>
-      <c r="C50">
-        <v>32.93493250867149</v>
       </c>
       <c r="D50">
         <v>4.229980555064522</v>
       </c>
       <c r="E50">
-        <v>15.09862011903809</v>
+        <v>21.03451036912483</v>
       </c>
       <c r="F50">
         <v>63.86686951183708</v>
       </c>
       <c r="G50">
-        <v>21.03451036912483</v>
+        <v>15.09862011903809</v>
       </c>
     </row>
     <row r="51">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="B51">
+        <v>30.85626124967858</v>
+      </c>
+      <c r="C51">
         <v>23.97360075426416</v>
-      </c>
-      <c r="C51">
-        <v>30.85626124967858</v>
       </c>
       <c r="D51">
         <v>4.171254915981408</v>
       </c>
       <c r="E51">
-        <v>15.48383525243578</v>
+        <v>19.92914083259522</v>
       </c>
       <c r="F51">
         <v>64.58702391496901</v>
       </c>
       <c r="G51">
-        <v>19.92914083259522</v>
+        <v>15.48383525243578</v>
       </c>
     </row>
     <row r="52">
@@ -1648,22 +1648,22 @@
         </is>
       </c>
       <c r="B52">
+        <v>31.79683306494901</v>
+      </c>
+      <c r="C52">
         <v>20.1154052603328</v>
-      </c>
-      <c r="C52">
-        <v>31.79683306494901</v>
       </c>
       <c r="D52">
         <v>4.971314209472982</v>
       </c>
       <c r="E52">
-        <v>13.24146459962016</v>
+        <v>20.93105428205468</v>
       </c>
       <c r="F52">
         <v>65.82748111832517</v>
       </c>
       <c r="G52">
-        <v>20.93105428205468</v>
+        <v>13.24146459962016</v>
       </c>
     </row>
     <row r="53">
@@ -1673,22 +1673,22 @@
         </is>
       </c>
       <c r="B53">
+        <v>31.26785538370604</v>
+      </c>
+      <c r="C53">
         <v>22.7662299280859</v>
-      </c>
-      <c r="C53">
-        <v>31.26785538370604</v>
       </c>
       <c r="D53">
         <v>4.392470791864993</v>
       </c>
       <c r="E53">
-        <v>14.77999488360194</v>
+        <v>20.29930928626247</v>
       </c>
       <c r="F53">
         <v>64.92069583013559</v>
       </c>
       <c r="G53">
-        <v>20.29930928626247</v>
+        <v>14.77999488360195</v>
       </c>
     </row>
   </sheetData>
